--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">disease</t>
   </si>
@@ -30,15 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">R_Squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norSMAPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norRMSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norMASE</t>
   </si>
   <si>
     <t xml:space="preserve">Index</t>
@@ -506,22 +497,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>11.59</v>
@@ -536,30 +518,21 @@
         <v>0.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.09</v>
+        <v>-0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
-        <v>14</v>
+      <c r="I2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>11.86</v>
@@ -574,30 +547,21 @@
         <v>0.57</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98</v>
+        <v>-0.75</v>
       </c>
       <c r="H3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>16.84</v>
@@ -612,30 +576,21 @@
         <v>0.24</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.01</v>
+        <v>-1.15</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>13.78</v>
@@ -650,30 +605,21 @@
         <v>0.59</v>
       </c>
       <c r="G5" t="n">
-        <v>0.21</v>
+        <v>-0.86</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>14.2</v>
@@ -688,30 +634,21 @@
         <v>0.46</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05</v>
+        <v>-0.95</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>14</v>
+      <c r="I6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>17.64</v>
@@ -726,30 +663,21 @@
         <v>0.34</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.33</v>
+        <v>-1.18</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-4.17</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>101.28</v>
@@ -764,30 +692,21 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.96</v>
+        <v>-18.85</v>
       </c>
       <c r="H8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>56.16</v>
@@ -802,30 +721,21 @@
         <v>0.33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.51</v>
+        <v>-2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>119.84</v>
@@ -840,30 +750,21 @@
         <v>0.02</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.56</v>
+        <v>-4.08</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>55.67</v>
@@ -878,30 +779,21 @@
         <v>0.47</v>
       </c>
       <c r="G11" t="n">
-        <v>0.53</v>
+        <v>-1.81</v>
       </c>
       <c r="H11" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>46.61</v>
@@ -916,30 +808,21 @@
         <v>0.18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.82</v>
+        <v>-1.17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="s">
-        <v>14</v>
+      <c r="I12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>51.69</v>
@@ -954,30 +837,21 @@
         <v>0.26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.66</v>
+        <v>-2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>25.44</v>
@@ -992,30 +866,21 @@
         <v>0.97</v>
       </c>
       <c r="G14" t="n">
-        <v>0.44</v>
+        <v>-1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>37.15</v>
@@ -1030,30 +895,21 @@
         <v>0.96</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.37</v>
+        <v>-1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>30.49</v>
@@ -1068,30 +924,21 @@
         <v>0.97</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.34</v>
+        <v>-1.28</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>33.53</v>
@@ -1106,30 +953,21 @@
         <v>0.96</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.81</v>
+        <v>-1.37</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-2.59</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>21.29</v>
@@ -1144,30 +982,21 @@
         <v>0.93</v>
       </c>
       <c r="G18" t="n">
-        <v>1.09</v>
+        <v>-1.13</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>21.95</v>
@@ -1182,30 +1011,21 @@
         <v>0.97</v>
       </c>
       <c r="G19" t="n">
-        <v>0.99</v>
+        <v>-1.08</v>
       </c>
       <c r="H19" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
         <v>20.01</v>
@@ -1220,30 +1040,21 @@
         <v>0.47</v>
       </c>
       <c r="G20" t="n">
-        <v>0.85</v>
+        <v>-2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
         <v>22.78</v>
@@ -1258,30 +1069,21 @@
         <v>0.6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.28</v>
+        <v>-2.74</v>
       </c>
       <c r="H21" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
         <v>24.48</v>
@@ -1296,30 +1098,21 @@
         <v>0.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08</v>
+        <v>-4.96</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
         <v>33.51</v>
@@ -1334,30 +1127,21 @@
         <v>0.29</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.95</v>
+        <v>-4.66</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-4.97</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
         <v>21.87</v>
@@ -1372,30 +1156,21 @@
         <v>0.57</v>
       </c>
       <c r="G24" t="n">
-        <v>0.47</v>
+        <v>-3.48</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
         <v>22.04</v>
@@ -1410,30 +1185,21 @@
         <v>0.35</v>
       </c>
       <c r="G25" t="n">
-        <v>0.43</v>
+        <v>-2.99</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
         <v>34.81</v>
@@ -1448,30 +1214,21 @@
         <v>0.73</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.03</v>
+        <v>-1.3</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C27" t="n">
         <v>33.35</v>
@@ -1486,30 +1243,21 @@
         <v>0.64</v>
       </c>
       <c r="G27" t="n">
-        <v>0.24</v>
+        <v>-1.38</v>
       </c>
       <c r="H27" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
         <v>24.59</v>
@@ -1524,30 +1272,21 @@
         <v>0.55</v>
       </c>
       <c r="G28" t="n">
-        <v>1.82</v>
+        <v>-0.96</v>
       </c>
       <c r="H28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="s">
-        <v>14</v>
+      <c r="I28" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C29" t="n">
         <v>36.23</v>
@@ -1562,30 +1301,21 @@
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.28</v>
+        <v>-1.45</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I29" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C30" t="n">
         <v>38.87</v>
@@ -1600,30 +1330,21 @@
         <v>0.58</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.76</v>
+        <v>-1.36</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C31" t="n">
         <v>40.2</v>
@@ -1638,30 +1359,21 @@
         <v>0.49</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>-1.83</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-3.39</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C32" t="n">
         <v>28.51</v>
@@ -1676,30 +1388,21 @@
         <v>0.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.75</v>
+        <v>-7.75</v>
       </c>
       <c r="H32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C33" t="n">
         <v>30.34</v>
@@ -1714,30 +1417,21 @@
         <v>0.15</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.04</v>
+        <v>-2.47</v>
       </c>
       <c r="H33" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C34" t="n">
         <v>29.55</v>
@@ -1752,30 +1446,21 @@
         <v>0.08</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3</v>
+        <v>-12.95</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C35" t="n">
         <v>34.72</v>
@@ -1790,30 +1475,21 @@
         <v>0.3</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.93</v>
+        <v>-1.24</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J35" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C36" t="n">
         <v>29.9</v>
@@ -1823,29 +1499,20 @@
       </c>
       <c r="E36"/>
       <c r="F36"/>
-      <c r="G36" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="G36"/>
       <c r="H36" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I36"/>
-      <c r="J36" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
         <v>28.45</v>
@@ -1860,30 +1527,21 @@
         <v>0.2</v>
       </c>
       <c r="G37" t="n">
-        <v>0.78</v>
+        <v>-3.51</v>
       </c>
       <c r="H37" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
         <v>14.81</v>
@@ -1898,30 +1556,21 @@
         <v>0.96</v>
       </c>
       <c r="G38" t="n">
-        <v>0.84</v>
+        <v>-0.62</v>
       </c>
       <c r="H38" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" t="n">
         <v>13.25</v>
@@ -1936,30 +1585,21 @@
         <v>0.96</v>
       </c>
       <c r="G39" t="n">
-        <v>0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="s">
-        <v>26</v>
+      <c r="I39" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C40" t="n">
         <v>40.97</v>
@@ -1974,30 +1614,21 @@
         <v>0.92</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.19</v>
+        <v>-2.72</v>
       </c>
       <c r="H40" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C41" t="n">
         <v>79.5</v>
@@ -2012,30 +1643,21 @@
         <v>0.56</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.71</v>
+        <v>-2.86</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C42" t="n">
         <v>21.83</v>
@@ -2050,30 +1672,21 @@
         <v>0.95</v>
       </c>
       <c r="G42" t="n">
-        <v>0.57</v>
+        <v>-1.11</v>
       </c>
       <c r="H42" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C43" t="n">
         <v>46.67</v>
@@ -2088,30 +1701,21 @@
         <v>0.65</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.42</v>
+        <v>-0.93</v>
       </c>
       <c r="H43" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
         <v>31.44</v>
@@ -2126,30 +1730,21 @@
         <v>0.91</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.64</v>
+        <v>-1.68</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J44" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C45" t="n">
         <v>34.28</v>
@@ -2164,30 +1759,21 @@
         <v>0.94</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.3</v>
+        <v>-1.81</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C46" t="n">
         <v>24.75</v>
@@ -2202,30 +1788,21 @@
         <v>0.88</v>
       </c>
       <c r="G46" t="n">
-        <v>0.91</v>
+        <v>-1.05</v>
       </c>
       <c r="H46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C47" t="n">
         <v>30.9</v>
@@ -2240,30 +1817,21 @@
         <v>0.77</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.51</v>
+        <v>-3.61</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J47" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C48" t="n">
         <v>22.95</v>
@@ -2278,30 +1846,21 @@
         <v>0.87</v>
       </c>
       <c r="G48" t="n">
-        <v>1.33</v>
+        <v>-0.96</v>
       </c>
       <c r="H48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="L48" t="s">
-        <v>26</v>
+      <c r="I48" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C49" t="n">
         <v>27.8</v>
@@ -2316,30 +1875,21 @@
         <v>0.92</v>
       </c>
       <c r="G49" t="n">
-        <v>0.21</v>
+        <v>-1.6</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
         <v>12.11</v>
@@ -2354,30 +1904,21 @@
         <v>0.93</v>
       </c>
       <c r="G50" t="n">
-        <v>1.07</v>
+        <v>-0.6</v>
       </c>
       <c r="H50" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="K50" t="n">
         <v>1</v>
       </c>
-      <c r="L50" t="s">
-        <v>26</v>
+      <c r="I50" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C51" t="n">
         <v>20.33</v>
@@ -2392,30 +1933,21 @@
         <v>0.91</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.56</v>
+        <v>-1.04</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="J51" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C52" t="n">
         <v>15.39</v>
@@ -2430,30 +1962,21 @@
         <v>0.89</v>
       </c>
       <c r="G52" t="n">
-        <v>0.02</v>
+        <v>-0.86</v>
       </c>
       <c r="H52" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C53" t="n">
         <v>15.18</v>
@@ -2468,30 +1991,21 @@
         <v>0.92</v>
       </c>
       <c r="G53" t="n">
-        <v>0.09</v>
+        <v>-0.76</v>
       </c>
       <c r="H53" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C54" t="n">
         <v>12.33</v>
@@ -2506,30 +2020,21 @@
         <v>0.92</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>-0.62</v>
       </c>
       <c r="H54" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C55" t="n">
         <v>17.41</v>
@@ -2544,30 +2049,21 @@
         <v>0.72</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.63</v>
+        <v>-1.2</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="J55" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C56" t="n">
         <v>24.92</v>
@@ -2582,30 +2078,21 @@
         <v>0.64</v>
       </c>
       <c r="G56" t="n">
-        <v>0.98</v>
+        <v>-1.24</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C57" t="n">
         <v>26.57</v>
@@ -2620,30 +2107,21 @@
         <v>0.63</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.38</v>
+        <v>-1.2</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J57" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C58" t="n">
         <v>24.64</v>
@@ -2658,30 +2136,21 @@
         <v>0.62</v>
       </c>
       <c r="G58" t="n">
-        <v>1.2</v>
+        <v>-1.15</v>
       </c>
       <c r="H58" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C59" t="n">
         <v>27.42</v>
@@ -2696,30 +2165,21 @@
         <v>0.73</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.08</v>
+        <v>-1.42</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="J59" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
         <v>27.42</v>
@@ -2734,30 +2194,21 @@
         <v>0.59</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.08</v>
+        <v>-1.22</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J60" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C61" t="n">
         <v>25.68</v>
@@ -2772,30 +2223,21 @@
         <v>0.63</v>
       </c>
       <c r="G61" t="n">
-        <v>0.35</v>
+        <v>-1.12</v>
       </c>
       <c r="H61" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C62" t="n">
         <v>10.8</v>
@@ -2810,30 +2252,21 @@
         <v>0.75</v>
       </c>
       <c r="G62" t="n">
-        <v>1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="H62" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C63" t="n">
         <v>19.8</v>
@@ -2848,30 +2281,21 @@
         <v>0.84</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.23</v>
+        <v>-1.34</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C64" t="n">
         <v>16.98</v>
@@ -2886,30 +2310,21 @@
         <v>0.9</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4</v>
+        <v>-1.42</v>
       </c>
       <c r="H64" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C65" t="n">
         <v>21.03</v>
@@ -2924,30 +2339,21 @@
         <v>0.9</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.51</v>
+        <v>-1.4</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="J65" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C66" t="n">
         <v>20.46</v>
@@ -2962,30 +2368,21 @@
         <v>0.88</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.38</v>
+        <v>-1.49</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J66" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I66" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
         <v>23.51</v>
@@ -3000,30 +2397,21 @@
         <v>0.82</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.07</v>
+        <v>-1.64</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J67" t="n">
-        <v>-2.76</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C68" t="n">
         <v>26.4</v>
@@ -3038,30 +2426,21 @@
         <v>0.77</v>
       </c>
       <c r="G68" t="n">
-        <v>-2</v>
+        <v>-1.46</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="J68" t="n">
-        <v>-5.53</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C69" t="n">
         <v>17.11</v>
@@ -3076,30 +2455,21 @@
         <v>0.8</v>
       </c>
       <c r="G69" t="n">
-        <v>0.12</v>
+        <v>-0.9</v>
       </c>
       <c r="H69" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="K69" t="n">
         <v>1</v>
       </c>
-      <c r="L69" t="s">
-        <v>26</v>
+      <c r="I69" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C70" t="n">
         <v>16.6</v>
@@ -3114,30 +2484,21 @@
         <v>0.78</v>
       </c>
       <c r="G70" t="n">
-        <v>0.24</v>
+        <v>-1.02</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C71" t="n">
         <v>16.06</v>
@@ -3152,30 +2513,21 @@
         <v>0.79</v>
       </c>
       <c r="G71" t="n">
-        <v>0.36</v>
+        <v>-1.01</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C72" t="n">
         <v>15</v>
@@ -3190,30 +2542,21 @@
         <v>0.82</v>
       </c>
       <c r="G72" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="H72" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I72" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C73" t="n">
         <v>14.76</v>
@@ -3228,30 +2571,21 @@
         <v>0.83</v>
       </c>
       <c r="G73" t="n">
-        <v>0.66</v>
+        <v>-0.94</v>
       </c>
       <c r="H73" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="I73" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C74" t="n">
         <v>42.31</v>
@@ -3266,30 +2600,21 @@
         <v>0.89</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.85</v>
+        <v>-0.7</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J74" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
         <v>27.57</v>
@@ -3304,30 +2629,21 @@
         <v>0.96</v>
       </c>
       <c r="G75" t="n">
-        <v>1.02</v>
+        <v>-0.44</v>
       </c>
       <c r="H75" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J75" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K75" t="n">
         <v>1</v>
       </c>
-      <c r="L75" t="s">
-        <v>33</v>
+      <c r="I75" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C76" t="n">
         <v>32.83</v>
@@ -3342,30 +2658,21 @@
         <v>0.75</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="I76" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="J76" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C77" t="n">
         <v>30.54</v>
@@ -3380,30 +2687,21 @@
         <v>0.84</v>
       </c>
       <c r="G77" t="n">
-        <v>0.44</v>
+        <v>-0.85</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C78" t="n">
         <v>33.63</v>
@@ -3418,30 +2716,21 @@
         <v>0.79</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.16</v>
+        <v>-0.92</v>
       </c>
       <c r="H78" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="J78" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I78" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C79" t="n">
         <v>30.01</v>
@@ -3456,30 +2745,21 @@
         <v>0.85</v>
       </c>
       <c r="G79" t="n">
-        <v>0.55</v>
+        <v>-0.67</v>
       </c>
       <c r="H79" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I79" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B80" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C80" t="n">
         <v>12.16</v>
@@ -3494,30 +2774,21 @@
         <v>0.48</v>
       </c>
       <c r="G80" t="n">
-        <v>1.06</v>
+        <v>-1.52</v>
       </c>
       <c r="H80" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I80" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C81" t="n">
         <v>28.45</v>
@@ -3532,30 +2803,21 @@
         <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.89</v>
+        <v>-9.97</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I81" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J81" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I81" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B82" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C82" t="n">
         <v>26.21</v>
@@ -3570,30 +2832,21 @@
         <v>0.82</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.63</v>
+        <v>-2.69</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J82" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I82" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C83" t="n">
         <v>29.78</v>
@@ -3608,30 +2861,21 @@
         <v>0.8</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.05</v>
+        <v>-2.92</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J83" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I83" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C84" t="n">
         <v>10.73</v>
@@ -3646,30 +2890,21 @@
         <v>0.64</v>
       </c>
       <c r="G84" t="n">
-        <v>1.23</v>
+        <v>-1.36</v>
       </c>
       <c r="H84" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J84" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="K84" t="n">
         <v>1</v>
       </c>
-      <c r="L84" t="s">
-        <v>33</v>
+      <c r="I84" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C85" t="n">
         <v>18.56</v>
@@ -3684,30 +2919,21 @@
         <v>0.67</v>
       </c>
       <c r="G85" t="n">
-        <v>0.29</v>
+        <v>-2.71</v>
       </c>
       <c r="H85" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I85" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C86" t="n">
         <v>35.17</v>
@@ -3722,30 +2948,21 @@
         <v>0.6</v>
       </c>
       <c r="G86" t="n">
-        <v>-1.05</v>
+        <v>-3.27</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I86" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J86" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I86" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C87" t="n">
         <v>29.87</v>
@@ -3760,30 +2977,21 @@
         <v>0.06</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.07</v>
+        <v>-3.25</v>
       </c>
       <c r="H87" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="I87" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="J87" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I87" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C88" t="n">
         <v>20.57</v>
@@ -3798,30 +3006,21 @@
         <v>0.49</v>
       </c>
       <c r="G88" t="n">
-        <v>1.65</v>
+        <v>-1.78</v>
       </c>
       <c r="H88" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J88" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="K88" t="n">
         <v>1</v>
       </c>
-      <c r="L88" t="s">
-        <v>33</v>
+      <c r="I88" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C89" t="n">
         <v>26.26</v>
@@ -3836,30 +3035,21 @@
         <v>0.56</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6</v>
+        <v>-2.3</v>
       </c>
       <c r="H89" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I89" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C90" t="n">
         <v>30.9</v>
@@ -3874,30 +3064,21 @@
         <v>0.4</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.26</v>
+        <v>-3.54</v>
       </c>
       <c r="H90" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I90" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="J90" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I90" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C91" t="n">
         <v>34.22</v>
@@ -3912,30 +3093,21 @@
         <v>0.65</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.87</v>
+        <v>-3.3</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I91" t="n">
-        <v>-0.56</v>
-      </c>
-      <c r="J91" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I91" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C92" t="n">
         <v>15.95</v>
@@ -3950,30 +3122,21 @@
         <v>0.39</v>
       </c>
       <c r="G92" t="n">
-        <v>1.03</v>
+        <v>-1.23</v>
       </c>
       <c r="H92" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J92" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="K92" t="n">
         <v>1</v>
       </c>
-      <c r="L92" t="s">
-        <v>33</v>
+      <c r="I92" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C93" t="n">
         <v>34.75</v>
@@ -3988,30 +3151,21 @@
         <v>0.76</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.37</v>
+        <v>-2.17</v>
       </c>
       <c r="H93" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="I93" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J93" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C94" t="n">
         <v>16.46</v>
@@ -4026,30 +3180,21 @@
         <v>0.67</v>
       </c>
       <c r="G94" t="n">
-        <v>0.96</v>
+        <v>-1.29</v>
       </c>
       <c r="H94" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I94" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
         <v>27.26</v>
@@ -4064,30 +3209,21 @@
         <v>0.69</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.42</v>
+        <v>-1.82</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C96" t="n">
         <v>19.35</v>
@@ -4102,30 +3238,21 @@
         <v>0.18</v>
       </c>
       <c r="G96" t="n">
-        <v>0.59</v>
+        <v>-2.74</v>
       </c>
       <c r="H96" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I96" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="J96" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I96" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C97" t="n">
         <v>30.14</v>
@@ -4140,30 +3267,21 @@
         <v>0.81</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.78</v>
+        <v>-2</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.69</v>
-      </c>
-      <c r="I97" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="J97" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I97" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C98" t="n">
         <v>11.01</v>
@@ -4178,30 +3296,21 @@
         <v>0.17</v>
       </c>
       <c r="G98" t="n">
-        <v>0.37</v>
+        <v>-3.8</v>
       </c>
       <c r="H98" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I98" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="J98" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I98" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
         <v>8.89</v>
@@ -4216,30 +3325,21 @@
         <v>0.63</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71</v>
+        <v>-0.69</v>
       </c>
       <c r="H99" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J99" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="K99" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I99" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C100" t="n">
         <v>13.25</v>
@@ -4254,30 +3354,21 @@
         <v>0.7</v>
       </c>
       <c r="G100" t="n">
-        <v>-1.05</v>
+        <v>-0.65</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J100" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I100" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C101" t="n">
         <v>13.01</v>
@@ -4292,30 +3383,21 @@
         <v>0.52</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.9</v>
+        <v>-0.77</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J101" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I101" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C102" t="n">
         <v>11.79</v>
@@ -4330,30 +3412,21 @@
         <v>0.72</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.13</v>
+        <v>-0.62</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J102" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="I102" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C103" t="n">
         <v>11.58</v>
@@ -4368,30 +3441,21 @@
         <v>0.24</v>
       </c>
       <c r="G103" t="n">
-        <v>0.01</v>
+        <v>-0.91</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J103" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="I103" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C104" t="n">
         <v>9.47</v>
@@ -4406,30 +3470,21 @@
         <v>0.54</v>
       </c>
       <c r="G104" t="n">
-        <v>0.47</v>
+        <v>-1.75</v>
       </c>
       <c r="H104" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J104" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I104" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C105" t="n">
         <v>13.48</v>
@@ -4444,30 +3499,21 @@
         <v>0.54</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.95</v>
+        <v>-2.12</v>
       </c>
       <c r="H105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J105" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I105" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C106" t="n">
         <v>10.79</v>
@@ -4482,30 +3528,21 @@
         <v>0.55</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I106" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C107" t="n">
         <v>14.76</v>
@@ -4520,30 +3557,21 @@
         <v>0.54</v>
       </c>
       <c r="G107" t="n">
-        <v>-1.41</v>
+        <v>-2.43</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J107" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I107" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C108" t="n">
         <v>7.47</v>
@@ -4558,30 +3586,21 @@
         <v>0.37</v>
       </c>
       <c r="G108" t="n">
-        <v>1.18</v>
+        <v>-6.06</v>
       </c>
       <c r="H108" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I108" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I108" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C109" t="n">
         <v>8.82</v>
@@ -4596,30 +3615,21 @@
         <v>0.44</v>
       </c>
       <c r="G109" t="n">
-        <v>0.7</v>
+        <v>-1.16</v>
       </c>
       <c r="H109" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J109" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="K109" t="n">
         <v>1</v>
       </c>
-      <c r="L109" t="s">
-        <v>39</v>
+      <c r="I109" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B110" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C110" t="n">
         <v>4.57</v>
@@ -4634,30 +3644,21 @@
         <v>0.78</v>
       </c>
       <c r="G110" t="n">
-        <v>0.72</v>
+        <v>-0.43</v>
       </c>
       <c r="H110" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J110" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="K110" t="n">
         <v>1</v>
       </c>
-      <c r="L110" t="s">
-        <v>39</v>
+      <c r="I110" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C111" t="n">
         <v>12.87</v>
@@ -4672,30 +3673,21 @@
         <v>0.28</v>
       </c>
       <c r="G111" t="n">
-        <v>0.28</v>
+        <v>-1</v>
       </c>
       <c r="H111" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I111" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I111" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C112" t="n">
         <v>56.07</v>
@@ -4710,30 +3702,21 @@
         <v>0.39</v>
       </c>
       <c r="G112" t="n">
-        <v>-2.01</v>
+        <v>-1.21</v>
       </c>
       <c r="H112" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="I112" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="J112" t="n">
-        <v>-5.11</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I112" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C113" t="n">
         <v>11.62</v>
@@ -4748,30 +3731,21 @@
         <v>0.47</v>
       </c>
       <c r="G113" t="n">
-        <v>0.35</v>
+        <v>-0.95</v>
       </c>
       <c r="H113" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I113" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I113" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C114" t="n">
         <v>10.44</v>
@@ -4786,30 +3760,21 @@
         <v>0.51</v>
       </c>
       <c r="G114" t="n">
-        <v>0.41</v>
+        <v>-0.72</v>
       </c>
       <c r="H114" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J114" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I114" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C115" t="n">
         <v>13.28</v>
@@ -4824,30 +3789,21 @@
         <v>0.4</v>
       </c>
       <c r="G115" t="n">
-        <v>0.26</v>
+        <v>-1.11</v>
       </c>
       <c r="H115" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I115" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="J115" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I115" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B116" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C116" t="n">
         <v>8.64</v>
@@ -4862,30 +3818,21 @@
         <v>0.84</v>
       </c>
       <c r="G116" t="n">
-        <v>-1.09</v>
+        <v>-0.84</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="I116" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="J116" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I116" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B117" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C117" t="n">
         <v>7.74</v>
@@ -4900,30 +3847,21 @@
         <v>0.85</v>
       </c>
       <c r="G117" t="n">
-        <v>0.25</v>
+        <v>-0.72</v>
       </c>
       <c r="H117" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I117" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I117" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C118" t="n">
         <v>8.38</v>
@@ -4938,30 +3876,21 @@
         <v>0.82</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="I118" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="J118" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I118" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C119" t="n">
         <v>7.57</v>
@@ -4976,30 +3905,21 @@
         <v>0.81</v>
       </c>
       <c r="G119" t="n">
-        <v>0.5</v>
+        <v>-0.63</v>
       </c>
       <c r="H119" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I119" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C120" t="n">
         <v>6.81</v>
@@ -5014,30 +3934,21 @@
         <v>0.83</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63</v>
+        <v>-0.56</v>
       </c>
       <c r="H120" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J120" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="K120" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I120" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C121" t="n">
         <v>8.29</v>
@@ -5052,30 +3963,21 @@
         <v>0.63</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.58</v>
+        <v>-0.48</v>
       </c>
       <c r="H121" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="I121" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J121" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="I121" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B122" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C122" t="n">
         <v>8.84</v>
@@ -5090,30 +3992,21 @@
         <v>0.72</v>
       </c>
       <c r="G122" t="n">
-        <v>0.42</v>
+        <v>-1.17</v>
       </c>
       <c r="H122" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I122" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I122" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B123" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C123" t="n">
         <v>12.49</v>
@@ -5128,30 +4021,21 @@
         <v>0.69</v>
       </c>
       <c r="G123" t="n">
-        <v>-1.98</v>
+        <v>-1.3</v>
       </c>
       <c r="H123" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="I123" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J123" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I123" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B124" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C124" t="n">
         <v>9.25</v>
@@ -5166,30 +4050,21 @@
         <v>0.68</v>
       </c>
       <c r="G124" t="n">
-        <v>0.15</v>
+        <v>-1.08</v>
       </c>
       <c r="H124" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I124" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C125" t="n">
         <v>8.66</v>
@@ -5204,30 +4079,21 @@
         <v>0.71</v>
       </c>
       <c r="G125" t="n">
-        <v>0.54</v>
+        <v>-0.9</v>
       </c>
       <c r="H125" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J125" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I125" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C126" t="n">
         <v>8.31</v>
@@ -5242,30 +4108,21 @@
         <v>0.81</v>
       </c>
       <c r="G126" t="n">
-        <v>0.77</v>
+        <v>-1.53</v>
       </c>
       <c r="H126" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I126" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="J126" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I126" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B127" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C127" t="n">
         <v>9.32</v>
@@ -5280,30 +4137,21 @@
         <v>0.55</v>
       </c>
       <c r="G127" t="n">
-        <v>0.1</v>
+        <v>-0.89</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I127" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J127" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="I127" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C128" t="n">
         <v>12.77</v>
@@ -5318,30 +4166,21 @@
         <v>0.01</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.48</v>
+        <v>-1.39</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J128" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="I128" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C129" t="n">
         <v>15.61</v>
@@ -5356,30 +4195,21 @@
         <v>0.02</v>
       </c>
       <c r="G129" t="n">
-        <v>-1.32</v>
+        <v>-1.66</v>
       </c>
       <c r="H129" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J129" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I129" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B130" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C130" t="n">
         <v>8.05</v>
@@ -5394,30 +4224,21 @@
         <v>0.07</v>
       </c>
       <c r="G130" t="n">
-        <v>0.92</v>
+        <v>-1.82</v>
       </c>
       <c r="H130" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J130" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="K130" t="n">
-        <v>1</v>
-      </c>
-      <c r="L130" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I130" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C131" t="n">
         <v>9.97</v>
@@ -5432,30 +4253,21 @@
         <v>0.03</v>
       </c>
       <c r="G131" t="n">
-        <v>0.35</v>
+        <v>-1.77</v>
       </c>
       <c r="H131" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I131" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B132" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C132" t="n">
         <v>13.52</v>
@@ -5470,30 +4282,21 @@
         <v>0.02</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.71</v>
+        <v>-1.54</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J132" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I132" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C133" t="n">
         <v>6.93</v>
@@ -5508,30 +4311,21 @@
         <v>0.11</v>
       </c>
       <c r="G133" t="n">
-        <v>1.25</v>
+        <v>-4.86</v>
       </c>
       <c r="H133" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I133" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I133" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C134" t="n">
         <v>7.62</v>
@@ -5546,30 +4340,21 @@
         <v>0.07</v>
       </c>
       <c r="G134" t="n">
-        <v>1.35</v>
+        <v>-0.98</v>
       </c>
       <c r="H134" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I134" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J134" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="K134" t="n">
         <v>1</v>
       </c>
-      <c r="L134" t="s">
-        <v>39</v>
+      <c r="I134" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C135" t="n">
         <v>16.2</v>
@@ -5584,30 +4369,21 @@
         <v>0.11</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.88</v>
+        <v>-1.85</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J135" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I135" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C136" t="n">
         <v>15.89</v>
@@ -5622,30 +4398,21 @@
         <v>0.13</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.8</v>
+        <v>-2.5</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="I136" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J136" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I136" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C137" t="n">
         <v>10.47</v>
@@ -5660,30 +4427,21 @@
         <v>0.11</v>
       </c>
       <c r="G137" t="n">
-        <v>0.61</v>
+        <v>-2.29</v>
       </c>
       <c r="H137" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I137" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J137" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I137" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C138" t="n">
         <v>16.54</v>
@@ -5698,30 +4456,21 @@
         <v>0.14</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.97</v>
+        <v>-2.53</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="I138" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="J138" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I138" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C139" t="n">
         <v>10.21</v>
@@ -5736,30 +4485,21 @@
         <v>0.01</v>
       </c>
       <c r="G139" t="n">
-        <v>0.68</v>
+        <v>-2.78</v>
       </c>
       <c r="H139" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I139" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I139" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C140" t="n">
         <v>71.22</v>
@@ -5774,30 +4514,21 @@
         <v>0.25</v>
       </c>
       <c r="G140" t="n">
-        <v>-2.03</v>
+        <v>-6.98</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="I140" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="J140" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I140" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C141" t="n">
         <v>30.24</v>
@@ -5812,30 +4543,21 @@
         <v>0.51</v>
       </c>
       <c r="G141" t="n">
-        <v>0.25</v>
+        <v>-3.17</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I141" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I141" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C142" t="n">
         <v>26.44</v>
@@ -5850,30 +4572,21 @@
         <v>0.68</v>
       </c>
       <c r="G142" t="n">
-        <v>0.47</v>
+        <v>-2.03</v>
       </c>
       <c r="H142" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J142" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="K142" t="n">
         <v>1</v>
       </c>
-      <c r="L142" t="s">
-        <v>39</v>
+      <c r="I142" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C143" t="n">
         <v>27.21</v>
@@ -5888,30 +4601,21 @@
         <v>0.58</v>
       </c>
       <c r="G143" t="n">
-        <v>0.42</v>
+        <v>-2.34</v>
       </c>
       <c r="H143" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J143" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I143" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B144" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C144" t="n">
         <v>26.52</v>
@@ -5926,30 +4630,21 @@
         <v>0.73</v>
       </c>
       <c r="G144" t="n">
-        <v>0.46</v>
+        <v>-2.09</v>
       </c>
       <c r="H144" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J144" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I144" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B145" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C145" t="n">
         <v>27.09</v>
@@ -5964,22 +4659,13 @@
         <v>0.53</v>
       </c>
       <c r="G145" t="n">
-        <v>0.43</v>
+        <v>-2.15</v>
       </c>
       <c r="H145" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J145" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I145" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">Pneumonia</t>
   </si>
   <si>
-    <t xml:space="preserve">TBATS</t>
+    <t xml:space="preserve">ETS</t>
   </si>
   <si>
     <t xml:space="preserve">Respiratory IDs</t>
   </si>
   <si>
+    <t xml:space="preserve">Neural Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBATS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARIMA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bayesian structural</t>
   </si>
   <si>
-    <t xml:space="preserve">Neural Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hybrid**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARIMA</t>
   </si>
   <si>
     <t xml:space="preserve">Influenza</t>
@@ -506,22 +506,22 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>11.59</v>
+        <v>13.78</v>
       </c>
       <c r="D2" t="n">
-        <v>3760.98</v>
+        <v>4515.34</v>
       </c>
       <c r="E2" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.75</v>
+        <v>-0.86</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -535,19 +535,19 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>11.86</v>
+        <v>17.65</v>
       </c>
       <c r="D3" t="n">
-        <v>4119.05</v>
+        <v>5427.33</v>
       </c>
       <c r="E3" t="n">
-        <v>0.75</v>
+        <v>1.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.75</v>
+        <v>-1.15</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -564,22 +564,22 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>16.84</v>
+        <v>11.59</v>
       </c>
       <c r="D4" t="n">
-        <v>5100.87</v>
+        <v>3760.98</v>
       </c>
       <c r="E4" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="F4" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.15</v>
+        <v>-0.75</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
@@ -593,19 +593,19 @@
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>13.78</v>
+        <v>17.64</v>
       </c>
       <c r="D5" t="n">
-        <v>4515.34</v>
+        <v>5826.04</v>
       </c>
       <c r="E5" t="n">
-        <v>0.86</v>
+        <v>1.18</v>
       </c>
       <c r="F5" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.86</v>
+        <v>-1.18</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -622,19 +622,19 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>14.2</v>
+        <v>11.86</v>
       </c>
       <c r="D6" t="n">
-        <v>4668.78</v>
+        <v>4119.05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="F6" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.95</v>
+        <v>-0.75</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -651,19 +651,19 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>17.64</v>
+        <v>14.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5826.04</v>
+        <v>4803.29</v>
       </c>
       <c r="E7" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="F7" t="n">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.18</v>
+        <v>-0.97</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>101.28</v>
+        <v>56.88</v>
       </c>
       <c r="D8" t="n">
-        <v>25326.8</v>
+        <v>16863.01</v>
       </c>
       <c r="E8" t="n">
-        <v>18.85</v>
+        <v>2.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="G8" t="n">
-        <v>-18.85</v>
+        <v>-2.4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -706,22 +706,22 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>56.16</v>
+        <v>103.34</v>
       </c>
       <c r="D9" t="n">
-        <v>16814.32</v>
+        <v>25636.96</v>
       </c>
       <c r="E9" t="n">
-        <v>2.36</v>
+        <v>19.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.36</v>
+        <v>-19.1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -735,7 +735,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>119.84</v>
@@ -767,22 +767,22 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.67</v>
+        <v>46.61</v>
       </c>
       <c r="D11" t="n">
-        <v>15505.1</v>
+        <v>17747.28</v>
       </c>
       <c r="E11" t="n">
-        <v>1.81</v>
+        <v>1.17</v>
       </c>
       <c r="F11" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.81</v>
+        <v>-1.17</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
@@ -796,22 +796,22 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>46.61</v>
+        <v>51.69</v>
       </c>
       <c r="D12" t="n">
-        <v>17747.28</v>
+        <v>16621.43</v>
       </c>
       <c r="E12" t="n">
-        <v>1.17</v>
+        <v>2.38</v>
       </c>
       <c r="F12" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.17</v>
+        <v>-2.38</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -822,22 +822,22 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>51.69</v>
+        <v>55.67</v>
       </c>
       <c r="D13" t="n">
-        <v>16621.43</v>
+        <v>15505.1</v>
       </c>
       <c r="E13" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="F13" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.38</v>
+        <v>-1.81</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -851,25 +851,25 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>25.44</v>
+        <v>19.2</v>
       </c>
       <c r="D14" t="n">
-        <v>2234.67</v>
+        <v>1316.98</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="F14" t="n">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2</v>
+        <v>-0.92</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
         <v>11</v>
@@ -880,22 +880,22 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>37.15</v>
+        <v>27.16</v>
       </c>
       <c r="D15" t="n">
-        <v>3190.05</v>
+        <v>2493.27</v>
       </c>
       <c r="E15" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="F15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.45</v>
+        <v>-1.23</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>30.49</v>
@@ -941,19 +941,19 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>33.53</v>
+        <v>21.95</v>
       </c>
       <c r="D17" t="n">
-        <v>3256.09</v>
+        <v>2067.97</v>
       </c>
       <c r="E17" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="F17" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.37</v>
+        <v>-1.08</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -967,22 +967,22 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>21.29</v>
+        <v>37.15</v>
       </c>
       <c r="D18" t="n">
-        <v>1201.94</v>
+        <v>3190.05</v>
       </c>
       <c r="E18" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="F18" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.13</v>
+        <v>-1.45</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -996,25 +996,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>21.95</v>
+        <v>33.53</v>
       </c>
       <c r="D19" t="n">
-        <v>2067.97</v>
+        <v>3256.09</v>
       </c>
       <c r="E19" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="F19" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.08</v>
+        <v>-1.37</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
         <v>11</v>
@@ -1025,22 +1025,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>20.01</v>
+        <v>33.51</v>
       </c>
       <c r="D20" t="n">
-        <v>49.74</v>
+        <v>71.07</v>
       </c>
       <c r="E20" t="n">
-        <v>2.92</v>
+        <v>4.66</v>
       </c>
       <c r="F20" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.92</v>
+        <v>-4.66</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>22.78</v>
+        <v>20.01</v>
       </c>
       <c r="D21" t="n">
-        <v>52.43</v>
+        <v>49.74</v>
       </c>
       <c r="E21" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.74</v>
+        <v>-2.92</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="s">
         <v>11</v>
@@ -1083,22 +1083,22 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>24.48</v>
+        <v>22.11</v>
       </c>
       <c r="D22" t="n">
-        <v>56.77</v>
+        <v>53.28</v>
       </c>
       <c r="E22" t="n">
-        <v>4.96</v>
+        <v>3.84</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.96</v>
+        <v>-3.84</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1115,19 +1115,19 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>33.51</v>
+        <v>25.05</v>
       </c>
       <c r="D23" t="n">
-        <v>71.07</v>
+        <v>58.07</v>
       </c>
       <c r="E23" t="n">
-        <v>4.66</v>
+        <v>5.47</v>
       </c>
       <c r="F23" t="n">
-        <v>0.29</v>
+        <v>0.69</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.66</v>
+        <v>-5.47</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>21.87</v>
+        <v>22.78</v>
       </c>
       <c r="D24" t="n">
-        <v>52.33</v>
+        <v>52.43</v>
       </c>
       <c r="E24" t="n">
-        <v>3.48</v>
+        <v>2.74</v>
       </c>
       <c r="F24" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.48</v>
+        <v>-2.74</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
         <v>11</v>
@@ -1170,7 +1170,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C25" t="n">
         <v>22.04</v>
@@ -1199,7 +1199,7 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
         <v>34.81</v>
@@ -1228,25 +1228,25 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>33.35</v>
+        <v>24.59</v>
       </c>
       <c r="D27" t="n">
-        <v>79.56</v>
+        <v>63.37</v>
       </c>
       <c r="E27" t="n">
-        <v>1.38</v>
+        <v>0.96</v>
       </c>
       <c r="F27" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.38</v>
+        <v>-0.96</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
         <v>11</v>
@@ -1257,25 +1257,25 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C28" t="n">
-        <v>24.59</v>
+        <v>38.87</v>
       </c>
       <c r="D28" t="n">
-        <v>63.37</v>
+        <v>98.87</v>
       </c>
       <c r="E28" t="n">
-        <v>0.96</v>
+        <v>1.36</v>
       </c>
       <c r="F28" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.96</v>
+        <v>-1.36</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="s">
         <v>11</v>
@@ -1286,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
         <v>36.23</v>
@@ -1318,19 +1318,19 @@
         <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>38.87</v>
+        <v>40.97</v>
       </c>
       <c r="D30" t="n">
-        <v>98.87</v>
+        <v>101.74</v>
       </c>
       <c r="E30" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="F30" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.36</v>
+        <v>-1.64</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>40.2</v>
+        <v>32.81</v>
       </c>
       <c r="D31" t="n">
-        <v>96.77</v>
+        <v>78.78</v>
       </c>
       <c r="E31" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="F31" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.83</v>
+        <v>-1.34</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1373,22 +1373,22 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>28.51</v>
+        <v>28.69</v>
       </c>
       <c r="D32" t="n">
-        <v>11.12</v>
+        <v>11.18</v>
       </c>
       <c r="E32" t="n">
-        <v>7.75</v>
+        <v>7.61</v>
       </c>
       <c r="F32" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="G32" t="n">
-        <v>-7.75</v>
+        <v>-7.61</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1402,22 +1402,22 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>30.34</v>
+        <v>31.22</v>
       </c>
       <c r="D33" t="n">
-        <v>11.83</v>
+        <v>12.67</v>
       </c>
       <c r="E33" t="n">
-        <v>2.47</v>
+        <v>7.11</v>
       </c>
       <c r="F33" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-2.47</v>
+        <v>-7.11</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1431,25 +1431,25 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>29.55</v>
+        <v>34.72</v>
       </c>
       <c r="D34" t="n">
-        <v>12.9</v>
+        <v>14.56</v>
       </c>
       <c r="E34" t="n">
-        <v>12.95</v>
+        <v>1.24</v>
       </c>
       <c r="F34" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="G34" t="n">
-        <v>-12.95</v>
+        <v>-1.24</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="s">
         <v>11</v>
@@ -1460,25 +1460,19 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>34.72</v>
+        <v>29.9</v>
       </c>
       <c r="D35" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-1.24</v>
-      </c>
+        <v>12.07</v>
+      </c>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="s">
         <v>11</v>
@@ -1492,14 +1486,20 @@
         <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>29.9</v>
+        <v>28.45</v>
       </c>
       <c r="D36" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
+        <v>11.04</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-3.51</v>
+      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
@@ -1512,22 +1512,22 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C37" t="n">
-        <v>28.45</v>
+        <v>30.34</v>
       </c>
       <c r="D37" t="n">
-        <v>11.04</v>
+        <v>11.83</v>
       </c>
       <c r="E37" t="n">
-        <v>3.51</v>
+        <v>2.47</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G37" t="n">
-        <v>-3.51</v>
+        <v>-2.47</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1544,22 +1544,22 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>14.81</v>
+        <v>13.25</v>
       </c>
       <c r="D38" t="n">
-        <v>1990.08</v>
+        <v>1528.12</v>
       </c>
       <c r="E38" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="F38" t="n">
         <v>0.96</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.62</v>
+        <v>-0.46</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="s">
         <v>23</v>
@@ -1570,25 +1570,25 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>13.25</v>
+        <v>14.81</v>
       </c>
       <c r="D39" t="n">
-        <v>1528.12</v>
+        <v>1990.08</v>
       </c>
       <c r="E39" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="F39" t="n">
         <v>0.96</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.46</v>
+        <v>-0.62</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="s">
         <v>23</v>
@@ -1602,19 +1602,19 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>40.97</v>
+        <v>23.42</v>
       </c>
       <c r="D40" t="n">
-        <v>5545.28</v>
+        <v>3241.35</v>
       </c>
       <c r="E40" t="n">
-        <v>2.72</v>
+        <v>0.97</v>
       </c>
       <c r="F40" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.72</v>
+        <v>-0.97</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C41" t="n">
         <v>79.5</v>
@@ -1657,22 +1657,22 @@
         <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="n">
-        <v>21.83</v>
+        <v>40.97</v>
       </c>
       <c r="D42" t="n">
-        <v>3252.11</v>
+        <v>5545.28</v>
       </c>
       <c r="E42" t="n">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="F42" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.11</v>
+        <v>-2.72</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1686,22 +1686,22 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>46.67</v>
+        <v>51.63</v>
       </c>
       <c r="D43" t="n">
-        <v>5151.77</v>
+        <v>5848.87</v>
       </c>
       <c r="E43" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="F43" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.93</v>
+        <v>-1.07</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1715,22 +1715,22 @@
         <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>31.44</v>
+        <v>27.92</v>
       </c>
       <c r="D44" t="n">
-        <v>73.25</v>
+        <v>69.61</v>
       </c>
       <c r="E44" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.68</v>
+        <v>-1.71</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1744,22 +1744,22 @@
         <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C45" t="n">
-        <v>34.28</v>
+        <v>30.7</v>
       </c>
       <c r="D45" t="n">
-        <v>74.45</v>
+        <v>89.63</v>
       </c>
       <c r="E45" t="n">
-        <v>1.81</v>
+        <v>3.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.94</v>
+        <v>0.78</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.81</v>
+        <v>-3.5</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1773,22 +1773,22 @@
         <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>24.75</v>
+        <v>31.44</v>
       </c>
       <c r="D46" t="n">
-        <v>55.03</v>
+        <v>73.25</v>
       </c>
       <c r="E46" t="n">
-        <v>1.05</v>
+        <v>1.68</v>
       </c>
       <c r="F46" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.05</v>
+        <v>-1.68</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1805,19 +1805,19 @@
         <v>13</v>
       </c>
       <c r="C47" t="n">
-        <v>30.9</v>
+        <v>24.75</v>
       </c>
       <c r="D47" t="n">
-        <v>90.2</v>
+        <v>55.03</v>
       </c>
       <c r="E47" t="n">
-        <v>3.61</v>
+        <v>1.05</v>
       </c>
       <c r="F47" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="G47" t="n">
-        <v>-3.61</v>
+        <v>-1.05</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C48" t="n">
         <v>22.95</v>
@@ -1860,22 +1860,22 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" t="n">
-        <v>27.8</v>
+        <v>34.28</v>
       </c>
       <c r="D49" t="n">
-        <v>67.83</v>
+        <v>74.45</v>
       </c>
       <c r="E49" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="F49" t="n">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="G49" t="n">
-        <v>-1.6</v>
+        <v>-1.81</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1892,22 +1892,22 @@
         <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>12.11</v>
+        <v>20.33</v>
       </c>
       <c r="D50" t="n">
-        <v>100.91</v>
+        <v>185.53</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="F50" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.6</v>
+        <v>-1.04</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="s">
         <v>23</v>
@@ -1918,22 +1918,22 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
-        <v>20.33</v>
+        <v>16.94</v>
       </c>
       <c r="D51" t="n">
-        <v>185.53</v>
+        <v>173.28</v>
       </c>
       <c r="E51" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.04</v>
+        <v>-1.2</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1947,25 +1947,25 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>15.39</v>
+        <v>12.11</v>
       </c>
       <c r="D52" t="n">
-        <v>140.05</v>
+        <v>100.91</v>
       </c>
       <c r="E52" t="n">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="F52" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.86</v>
+        <v>-0.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="s">
         <v>23</v>
@@ -1976,22 +1976,22 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C53" t="n">
-        <v>15.18</v>
+        <v>12.33</v>
       </c>
       <c r="D53" t="n">
-        <v>132.61</v>
+        <v>112.01</v>
       </c>
       <c r="E53" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="F53" t="n">
         <v>0.92</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.76</v>
+        <v>-0.62</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2005,22 +2005,22 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C54" t="n">
-        <v>12.33</v>
+        <v>15.18</v>
       </c>
       <c r="D54" t="n">
-        <v>112.01</v>
+        <v>132.61</v>
       </c>
       <c r="E54" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="F54" t="n">
         <v>0.92</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.62</v>
+        <v>-0.76</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2034,22 +2034,22 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>17.41</v>
+        <v>15.27</v>
       </c>
       <c r="D55" t="n">
-        <v>175.38</v>
+        <v>138.16</v>
       </c>
       <c r="E55" t="n">
-        <v>1.2</v>
+        <v>0.84</v>
       </c>
       <c r="F55" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.2</v>
+        <v>-0.84</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2066,22 +2066,22 @@
         <v>15</v>
       </c>
       <c r="C56" t="n">
-        <v>24.92</v>
+        <v>25.68</v>
       </c>
       <c r="D56" t="n">
-        <v>80.61</v>
+        <v>71.81</v>
       </c>
       <c r="E56" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="F56" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="s">
         <v>23</v>
@@ -2092,7 +2092,7 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
         <v>26.57</v>
@@ -2121,22 +2121,22 @@
         <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C58" t="n">
-        <v>24.64</v>
+        <v>27.42</v>
       </c>
       <c r="D58" t="n">
-        <v>72.51</v>
+        <v>88.5</v>
       </c>
       <c r="E58" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="F58" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.15</v>
+        <v>-1.22</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2150,22 +2150,22 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C59" t="n">
-        <v>27.42</v>
+        <v>24.64</v>
       </c>
       <c r="D59" t="n">
-        <v>83.15</v>
+        <v>72.51</v>
       </c>
       <c r="E59" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="F59" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.42</v>
+        <v>-1.15</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2179,22 +2179,22 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C60" t="n">
-        <v>27.42</v>
+        <v>26.77</v>
       </c>
       <c r="D60" t="n">
-        <v>88.5</v>
+        <v>82.1</v>
       </c>
       <c r="E60" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="F60" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.22</v>
+        <v>-1.42</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2208,25 +2208,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>25.68</v>
+        <v>25.07</v>
       </c>
       <c r="D61" t="n">
-        <v>71.81</v>
+        <v>80.24</v>
       </c>
       <c r="E61" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="F61" t="n">
         <v>0.63</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.12</v>
+        <v>-1.22</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="s">
         <v>23</v>
@@ -2237,22 +2237,22 @@
         <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C62" t="n">
-        <v>10.8</v>
+        <v>20.46</v>
       </c>
       <c r="D62" t="n">
-        <v>29.7</v>
+        <v>45.6</v>
       </c>
       <c r="E62" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="F62" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="G62" t="n">
-        <v>-1.9</v>
+        <v>-1.49</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2266,25 +2266,25 @@
         <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>19.8</v>
+        <v>9.97</v>
       </c>
       <c r="D63" t="n">
-        <v>45.1</v>
+        <v>26.23</v>
       </c>
       <c r="E63" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="F63" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="G63" t="n">
-        <v>-1.34</v>
+        <v>-1.48</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="s">
         <v>23</v>
@@ -2295,22 +2295,22 @@
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="n">
-        <v>16.98</v>
+        <v>21.03</v>
       </c>
       <c r="D64" t="n">
-        <v>39.92</v>
+        <v>46.49</v>
       </c>
       <c r="E64" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="F64" t="n">
         <v>0.9</v>
       </c>
       <c r="G64" t="n">
-        <v>-1.42</v>
+        <v>-1.4</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2324,22 +2324,22 @@
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C65" t="n">
-        <v>21.03</v>
+        <v>23.51</v>
       </c>
       <c r="D65" t="n">
-        <v>46.49</v>
+        <v>52.04</v>
       </c>
       <c r="E65" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.4</v>
+        <v>-1.64</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2356,22 +2356,22 @@
         <v>14</v>
       </c>
       <c r="C66" t="n">
-        <v>20.46</v>
+        <v>19.8</v>
       </c>
       <c r="D66" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="E66" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="F66" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.49</v>
+        <v>-1.34</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="s">
         <v>23</v>
@@ -2382,22 +2382,22 @@
         <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>23.51</v>
+        <v>15.79</v>
       </c>
       <c r="D67" t="n">
-        <v>52.04</v>
+        <v>37.89</v>
       </c>
       <c r="E67" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="F67" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.64</v>
+        <v>-1.37</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2411,22 +2411,22 @@
         <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>26.4</v>
+        <v>16.06</v>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.51</v>
       </c>
       <c r="E68" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="F68" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.46</v>
+        <v>-1.01</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2440,25 +2440,25 @@
         <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C69" t="n">
-        <v>17.11</v>
+        <v>29.15</v>
       </c>
       <c r="D69" t="n">
-        <v>10.16</v>
+        <v>13.39</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9</v>
+        <v>1.81</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.9</v>
+        <v>-1.81</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="s">
         <v>23</v>
@@ -2469,25 +2469,25 @@
         <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C70" t="n">
-        <v>16.6</v>
+        <v>17.11</v>
       </c>
       <c r="D70" t="n">
-        <v>11.49</v>
+        <v>10.16</v>
       </c>
       <c r="E70" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="F70" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.02</v>
+        <v>-0.9</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="s">
         <v>23</v>
@@ -2498,22 +2498,22 @@
         <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71" t="n">
-        <v>16.06</v>
+        <v>15</v>
       </c>
       <c r="D71" t="n">
-        <v>11.51</v>
+        <v>11.24</v>
       </c>
       <c r="E71" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="F71" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.01</v>
+        <v>-0.95</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
         <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>15</v>
+        <v>15.58</v>
       </c>
       <c r="D72" t="n">
-        <v>11.24</v>
+        <v>11.31</v>
       </c>
       <c r="E72" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.95</v>
+        <v>-1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2559,19 +2559,19 @@
         <v>15</v>
       </c>
       <c r="C73" t="n">
-        <v>14.76</v>
+        <v>16.6</v>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.49</v>
       </c>
       <c r="E73" t="n">
-        <v>0.94</v>
+        <v>1.02</v>
       </c>
       <c r="F73" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.94</v>
+        <v>-1.02</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2585,22 +2585,22 @@
         <v>29</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C74" t="n">
-        <v>42.31</v>
+        <v>30.54</v>
       </c>
       <c r="D74" t="n">
-        <v>3173.73</v>
+        <v>2016.4</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F74" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.7</v>
+        <v>-0.85</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2614,25 +2614,25 @@
         <v>29</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C75" t="n">
-        <v>27.57</v>
+        <v>32.83</v>
       </c>
       <c r="D75" t="n">
-        <v>1575.93</v>
+        <v>3120.22</v>
       </c>
       <c r="E75" t="n">
-        <v>0.44</v>
+        <v>1.56</v>
       </c>
       <c r="F75" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.44</v>
+        <v>-1.56</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="s">
         <v>30</v>
@@ -2646,19 +2646,19 @@
         <v>14</v>
       </c>
       <c r="C76" t="n">
-        <v>32.83</v>
+        <v>42.31</v>
       </c>
       <c r="D76" t="n">
-        <v>3120.22</v>
+        <v>3173.73</v>
       </c>
       <c r="E76" t="n">
-        <v>1.56</v>
+        <v>0.7</v>
       </c>
       <c r="F76" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.56</v>
+        <v>-0.7</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2675,19 +2675,19 @@
         <v>12</v>
       </c>
       <c r="C77" t="n">
-        <v>30.54</v>
+        <v>33.68</v>
       </c>
       <c r="D77" t="n">
-        <v>2016.4</v>
+        <v>3047.22</v>
       </c>
       <c r="E77" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="F77" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.85</v>
+        <v>-0.63</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2701,25 +2701,25 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>33.63</v>
+        <v>31.16</v>
       </c>
       <c r="D78" t="n">
-        <v>2109.09</v>
+        <v>1895.72</v>
       </c>
       <c r="E78" t="n">
-        <v>0.92</v>
+        <v>0.61</v>
       </c>
       <c r="F78" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.92</v>
+        <v>-0.61</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="s">
         <v>30</v>
@@ -2730,22 +2730,22 @@
         <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="n">
-        <v>30.01</v>
+        <v>33.63</v>
       </c>
       <c r="D79" t="n">
-        <v>1756.65</v>
+        <v>2109.09</v>
       </c>
       <c r="E79" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="F79" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.67</v>
+        <v>-0.92</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2759,22 +2759,22 @@
         <v>31</v>
       </c>
       <c r="B80" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C80" t="n">
-        <v>12.16</v>
+        <v>27.34</v>
       </c>
       <c r="D80" t="n">
-        <v>25.68</v>
+        <v>51.86</v>
       </c>
       <c r="E80" t="n">
-        <v>1.52</v>
+        <v>8.33</v>
       </c>
       <c r="F80" t="n">
-        <v>0.48</v>
+        <v>0.01</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.52</v>
+        <v>-8.33</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2791,22 +2791,22 @@
         <v>13</v>
       </c>
       <c r="C81" t="n">
-        <v>28.45</v>
+        <v>10.73</v>
       </c>
       <c r="D81" t="n">
-        <v>51.29</v>
+        <v>21.91</v>
       </c>
       <c r="E81" t="n">
-        <v>9.97</v>
+        <v>1.36</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="G81" t="n">
-        <v>-9.97</v>
+        <v>-1.36</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="s">
         <v>30</v>
@@ -2820,19 +2820,19 @@
         <v>14</v>
       </c>
       <c r="C82" t="n">
-        <v>26.21</v>
+        <v>12.16</v>
       </c>
       <c r="D82" t="n">
-        <v>47.93</v>
+        <v>25.68</v>
       </c>
       <c r="E82" t="n">
-        <v>2.69</v>
+        <v>1.52</v>
       </c>
       <c r="F82" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="G82" t="n">
-        <v>-2.69</v>
+        <v>-1.52</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C83" t="n">
         <v>29.78</v>
@@ -2878,22 +2878,22 @@
         <v>10</v>
       </c>
       <c r="C84" t="n">
-        <v>10.73</v>
+        <v>26.21</v>
       </c>
       <c r="D84" t="n">
-        <v>21.91</v>
+        <v>47.93</v>
       </c>
       <c r="E84" t="n">
-        <v>1.36</v>
+        <v>2.69</v>
       </c>
       <c r="F84" t="n">
-        <v>0.64</v>
+        <v>0.82</v>
       </c>
       <c r="G84" t="n">
-        <v>-1.36</v>
+        <v>-2.69</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="s">
         <v>30</v>
@@ -2904,22 +2904,22 @@
         <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>18.56</v>
+        <v>19.15</v>
       </c>
       <c r="D85" t="n">
-        <v>33.26</v>
+        <v>34.25</v>
       </c>
       <c r="E85" t="n">
-        <v>2.71</v>
+        <v>3.06</v>
       </c>
       <c r="F85" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G85" t="n">
-        <v>-2.71</v>
+        <v>-3.06</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2933,25 +2933,25 @@
         <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>35.17</v>
+        <v>20.57</v>
       </c>
       <c r="D86" t="n">
-        <v>28.81</v>
+        <v>19.83</v>
       </c>
       <c r="E86" t="n">
-        <v>3.27</v>
+        <v>1.78</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="G86" t="n">
-        <v>-3.27</v>
+        <v>-1.78</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="s">
         <v>30</v>
@@ -2962,22 +2962,22 @@
         <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C87" t="n">
-        <v>29.87</v>
+        <v>26.26</v>
       </c>
       <c r="D87" t="n">
-        <v>36.24</v>
+        <v>22.54</v>
       </c>
       <c r="E87" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="F87" t="n">
-        <v>0.06</v>
+        <v>0.56</v>
       </c>
       <c r="G87" t="n">
-        <v>-3.25</v>
+        <v>-2.3</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2991,25 +2991,25 @@
         <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C88" t="n">
-        <v>20.57</v>
+        <v>34.22</v>
       </c>
       <c r="D88" t="n">
-        <v>19.83</v>
+        <v>27.65</v>
       </c>
       <c r="E88" t="n">
-        <v>1.78</v>
+        <v>3.3</v>
       </c>
       <c r="F88" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="G88" t="n">
-        <v>-1.78</v>
+        <v>-3.3</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="s">
         <v>30</v>
@@ -3020,22 +3020,22 @@
         <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>26.26</v>
+        <v>35.17</v>
       </c>
       <c r="D89" t="n">
-        <v>22.54</v>
+        <v>28.81</v>
       </c>
       <c r="E89" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="F89" t="n">
-        <v>0.56</v>
+        <v>0.6</v>
       </c>
       <c r="G89" t="n">
-        <v>-2.3</v>
+        <v>-3.27</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3049,22 +3049,22 @@
         <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C90" t="n">
-        <v>30.9</v>
+        <v>25.93</v>
       </c>
       <c r="D90" t="n">
-        <v>26.24</v>
+        <v>25.63</v>
       </c>
       <c r="E90" t="n">
-        <v>3.54</v>
+        <v>3.89</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="G90" t="n">
-        <v>-3.54</v>
+        <v>-3.89</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3078,19 +3078,19 @@
         <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>34.22</v>
+        <v>29.31</v>
       </c>
       <c r="D91" t="n">
-        <v>27.65</v>
+        <v>24.97</v>
       </c>
       <c r="E91" t="n">
         <v>3.3</v>
       </c>
       <c r="F91" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="G91" t="n">
         <v>-3.3</v>
@@ -3107,25 +3107,25 @@
         <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C92" t="n">
-        <v>15.95</v>
+        <v>27.26</v>
       </c>
       <c r="D92" t="n">
-        <v>18.2</v>
+        <v>29.44</v>
       </c>
       <c r="E92" t="n">
-        <v>1.23</v>
+        <v>1.82</v>
       </c>
       <c r="F92" t="n">
-        <v>0.39</v>
+        <v>0.69</v>
       </c>
       <c r="G92" t="n">
-        <v>-1.23</v>
+        <v>-1.82</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="s">
         <v>30</v>
@@ -3136,22 +3136,22 @@
         <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C93" t="n">
-        <v>34.75</v>
+        <v>15.95</v>
       </c>
       <c r="D93" t="n">
-        <v>37.77</v>
+        <v>18.2</v>
       </c>
       <c r="E93" t="n">
-        <v>2.17</v>
+        <v>1.23</v>
       </c>
       <c r="F93" t="n">
-        <v>0.76</v>
+        <v>0.39</v>
       </c>
       <c r="G93" t="n">
-        <v>-2.17</v>
+        <v>-1.23</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3165,22 +3165,22 @@
         <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C94" t="n">
-        <v>16.46</v>
+        <v>19.42</v>
       </c>
       <c r="D94" t="n">
-        <v>17.98</v>
+        <v>20.85</v>
       </c>
       <c r="E94" t="n">
-        <v>1.29</v>
+        <v>2.84</v>
       </c>
       <c r="F94" t="n">
-        <v>0.67</v>
+        <v>0.18</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.29</v>
+        <v>-2.84</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3194,25 +3194,25 @@
         <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>27.26</v>
+        <v>14.78</v>
       </c>
       <c r="D95" t="n">
-        <v>29.44</v>
+        <v>17.03</v>
       </c>
       <c r="E95" t="n">
-        <v>1.82</v>
+        <v>1.21</v>
       </c>
       <c r="F95" t="n">
-        <v>0.69</v>
+        <v>0.63</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.82</v>
+        <v>-1.21</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="s">
         <v>30</v>
@@ -3223,22 +3223,22 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>19.35</v>
+        <v>34.75</v>
       </c>
       <c r="D96" t="n">
-        <v>20.86</v>
+        <v>37.77</v>
       </c>
       <c r="E96" t="n">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="F96" t="n">
-        <v>0.18</v>
+        <v>0.76</v>
       </c>
       <c r="G96" t="n">
-        <v>-2.74</v>
+        <v>-2.17</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C97" t="n">
         <v>30.14</v>
@@ -3281,22 +3281,22 @@
         <v>34</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C98" t="n">
-        <v>11.01</v>
+        <v>11.58</v>
       </c>
       <c r="D98" t="n">
-        <v>5.01</v>
+        <v>5.47</v>
       </c>
       <c r="E98" t="n">
-        <v>3.8</v>
+        <v>0.91</v>
       </c>
       <c r="F98" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="G98" t="n">
-        <v>-3.8</v>
+        <v>-0.91</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3310,22 +3310,22 @@
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C99" t="n">
-        <v>8.89</v>
+        <v>10.22</v>
       </c>
       <c r="D99" t="n">
-        <v>3.5</v>
+        <v>4.78</v>
       </c>
       <c r="E99" t="n">
-        <v>0.69</v>
+        <v>1.73</v>
       </c>
       <c r="F99" t="n">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.69</v>
+        <v>-1.73</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3339,25 +3339,25 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C100" t="n">
-        <v>13.25</v>
+        <v>11.79</v>
       </c>
       <c r="D100" t="n">
-        <v>5.68</v>
+        <v>5.44</v>
       </c>
       <c r="E100" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="s">
         <v>30</v>
@@ -3368,22 +3368,22 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>13.01</v>
+        <v>13.25</v>
       </c>
       <c r="D101" t="n">
-        <v>5.49</v>
+        <v>5.68</v>
       </c>
       <c r="E101" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="F101" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.77</v>
+        <v>-0.65</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3397,25 +3397,25 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C102" t="n">
-        <v>11.79</v>
+        <v>13.01</v>
       </c>
       <c r="D102" t="n">
-        <v>5.44</v>
+        <v>5.49</v>
       </c>
       <c r="E102" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="F102" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.62</v>
+        <v>-0.77</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
         <v>30</v>
@@ -3429,19 +3429,19 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>11.58</v>
+        <v>8.08</v>
       </c>
       <c r="D103" t="n">
-        <v>5.47</v>
+        <v>3.19</v>
       </c>
       <c r="E103" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="F103" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3455,22 +3455,22 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104" t="n">
-        <v>9.47</v>
+        <v>13.48</v>
       </c>
       <c r="D104" t="n">
-        <v>90.13</v>
+        <v>127.7</v>
       </c>
       <c r="E104" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="F104" t="n">
         <v>0.54</v>
       </c>
       <c r="G104" t="n">
-        <v>-1.75</v>
+        <v>-2.12</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3484,22 +3484,22 @@
         <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C105" t="n">
-        <v>13.48</v>
+        <v>6.09</v>
       </c>
       <c r="D105" t="n">
-        <v>127.7</v>
+        <v>60.99</v>
       </c>
       <c r="E105" t="n">
-        <v>2.12</v>
+        <v>4.98</v>
       </c>
       <c r="F105" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="G105" t="n">
-        <v>-2.12</v>
+        <v>-4.98</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C106" t="n">
         <v>10.79</v>
@@ -3542,7 +3542,7 @@
         <v>35</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C107" t="n">
         <v>14.76</v>
@@ -3574,22 +3574,22 @@
         <v>13</v>
       </c>
       <c r="C108" t="n">
-        <v>7.47</v>
+        <v>8.82</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59</v>
+        <v>88.54</v>
       </c>
       <c r="E108" t="n">
-        <v>6.06</v>
+        <v>1.16</v>
       </c>
       <c r="F108" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="G108" t="n">
-        <v>-6.06</v>
+        <v>-1.16</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" t="s">
         <v>36</v>
@@ -3600,25 +3600,25 @@
         <v>35</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>8.82</v>
+        <v>9.44</v>
       </c>
       <c r="D109" t="n">
-        <v>88.54</v>
+        <v>90.42</v>
       </c>
       <c r="E109" t="n">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="F109" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="G109" t="n">
-        <v>-1.16</v>
+        <v>-1.67</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="s">
         <v>36</v>
@@ -3629,25 +3629,25 @@
         <v>37</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C110" t="n">
-        <v>4.57</v>
+        <v>38.29</v>
       </c>
       <c r="D110" t="n">
-        <v>43.36</v>
+        <v>508.07</v>
       </c>
       <c r="E110" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="F110" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.43</v>
+        <v>-1.08</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="s">
         <v>36</v>
@@ -3658,25 +3658,25 @@
         <v>37</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C111" t="n">
-        <v>12.87</v>
+        <v>4.57</v>
       </c>
       <c r="D111" t="n">
-        <v>110.82</v>
+        <v>43.36</v>
       </c>
       <c r="E111" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="H111" t="n">
         <v>1</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G111" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
       </c>
       <c r="I111" t="s">
         <v>36</v>
@@ -3687,22 +3687,22 @@
         <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>56.07</v>
+        <v>10.01</v>
       </c>
       <c r="D112" t="n">
-        <v>853.08</v>
+        <v>104.79</v>
       </c>
       <c r="E112" t="n">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="F112" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="G112" t="n">
-        <v>-1.21</v>
+        <v>-0.71</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3716,22 +3716,22 @@
         <v>37</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C113" t="n">
-        <v>11.62</v>
+        <v>12.87</v>
       </c>
       <c r="D113" t="n">
-        <v>95.18</v>
+        <v>110.82</v>
       </c>
       <c r="E113" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.95</v>
+        <v>-1</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
         <v>37</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C114" t="n">
-        <v>10.44</v>
+        <v>11.62</v>
       </c>
       <c r="D114" t="n">
-        <v>119.9</v>
+        <v>95.18</v>
       </c>
       <c r="E114" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="F114" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.72</v>
+        <v>-0.95</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>37</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C115" t="n">
         <v>13.28</v>
@@ -3803,22 +3803,22 @@
         <v>38</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C116" t="n">
-        <v>8.64</v>
+        <v>8.38</v>
       </c>
       <c r="D116" t="n">
-        <v>63.09</v>
+        <v>63.81</v>
       </c>
       <c r="E116" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="F116" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.84</v>
+        <v>-0.67</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3835,19 +3835,19 @@
         <v>14</v>
       </c>
       <c r="C117" t="n">
-        <v>7.74</v>
+        <v>8.64</v>
       </c>
       <c r="D117" t="n">
-        <v>58.69</v>
+        <v>63.09</v>
       </c>
       <c r="E117" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="F117" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.72</v>
+        <v>-0.84</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3861,22 +3861,22 @@
         <v>38</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C118" t="n">
-        <v>8.38</v>
+        <v>7.57</v>
       </c>
       <c r="D118" t="n">
-        <v>63.81</v>
+        <v>60.99</v>
       </c>
       <c r="E118" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="F118" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.67</v>
+        <v>-0.63</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3893,19 +3893,19 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>7.57</v>
+        <v>7.74</v>
       </c>
       <c r="D119" t="n">
-        <v>60.99</v>
+        <v>58.69</v>
       </c>
       <c r="E119" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="F119" t="n">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.63</v>
+        <v>-0.72</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3919,25 +3919,25 @@
         <v>38</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C120" t="n">
-        <v>6.81</v>
+        <v>8.15</v>
       </c>
       <c r="D120" t="n">
-        <v>56.71</v>
+        <v>61.36</v>
       </c>
       <c r="E120" t="n">
-        <v>0.56</v>
+        <v>0.53</v>
       </c>
       <c r="F120" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.56</v>
+        <v>-0.53</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="s">
         <v>36</v>
@@ -3948,25 +3948,25 @@
         <v>38</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>8.29</v>
+        <v>7.18</v>
       </c>
       <c r="D121" t="n">
-        <v>65.58</v>
+        <v>57.42</v>
       </c>
       <c r="E121" t="n">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="F121" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.48</v>
+        <v>-0.62</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" t="s">
         <v>36</v>
@@ -3980,19 +3980,19 @@
         <v>15</v>
       </c>
       <c r="C122" t="n">
-        <v>8.84</v>
+        <v>8.66</v>
       </c>
       <c r="D122" t="n">
-        <v>38.28</v>
+        <v>37.72</v>
       </c>
       <c r="E122" t="n">
-        <v>1.17</v>
+        <v>0.9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G122" t="n">
-        <v>-1.17</v>
+        <v>-0.9</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
         <v>39</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C123" t="n">
         <v>12.49</v>
@@ -4035,25 +4035,25 @@
         <v>39</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C124" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
       <c r="D124" t="n">
-        <v>39.98</v>
+        <v>42.19</v>
       </c>
       <c r="E124" t="n">
-        <v>1.08</v>
+        <v>0.89</v>
       </c>
       <c r="F124" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="G124" t="n">
-        <v>-1.08</v>
+        <v>-0.89</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="s">
         <v>36</v>
@@ -4067,19 +4067,19 @@
         <v>12</v>
       </c>
       <c r="C125" t="n">
-        <v>8.66</v>
+        <v>7.84</v>
       </c>
       <c r="D125" t="n">
-        <v>37.72</v>
+        <v>34.29</v>
       </c>
       <c r="E125" t="n">
-        <v>0.9</v>
+        <v>1.47</v>
       </c>
       <c r="F125" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.9</v>
+        <v>-1.47</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4093,22 +4093,22 @@
         <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C126" t="n">
-        <v>8.31</v>
+        <v>9.25</v>
       </c>
       <c r="D126" t="n">
-        <v>37.94</v>
+        <v>39.98</v>
       </c>
       <c r="E126" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="F126" t="n">
-        <v>0.81</v>
+        <v>0.68</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.53</v>
+        <v>-1.08</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4122,25 +4122,25 @@
         <v>39</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>9.32</v>
+        <v>8</v>
       </c>
       <c r="D127" t="n">
-        <v>42.19</v>
+        <v>34.97</v>
       </c>
       <c r="E127" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="F127" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.89</v>
+        <v>-1.17</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="s">
         <v>36</v>
@@ -4151,25 +4151,25 @@
         <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>12.77</v>
+        <v>6.88</v>
       </c>
       <c r="D128" t="n">
-        <v>24.9</v>
+        <v>16.38</v>
       </c>
       <c r="E128" t="n">
-        <v>1.39</v>
+        <v>4.73</v>
       </c>
       <c r="F128" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="G128" t="n">
-        <v>-1.39</v>
+        <v>-4.73</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="s">
         <v>36</v>
@@ -4180,22 +4180,22 @@
         <v>40</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>15.61</v>
+        <v>9.59</v>
       </c>
       <c r="D129" t="n">
-        <v>29.31</v>
+        <v>19.02</v>
       </c>
       <c r="E129" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G129" t="n">
-        <v>-1.66</v>
+        <v>-1.81</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4209,22 +4209,22 @@
         <v>40</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C130" t="n">
-        <v>8.05</v>
+        <v>15.61</v>
       </c>
       <c r="D130" t="n">
-        <v>16.82</v>
+        <v>29.31</v>
       </c>
       <c r="E130" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="F130" t="n">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
       <c r="G130" t="n">
-        <v>-1.82</v>
+        <v>-1.66</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4238,25 +4238,25 @@
         <v>40</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>9.97</v>
+        <v>12.77</v>
       </c>
       <c r="D131" t="n">
-        <v>19.56</v>
+        <v>24.9</v>
       </c>
       <c r="E131" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="F131" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G131" t="n">
-        <v>-1.77</v>
+        <v>-1.39</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="s">
         <v>36</v>
@@ -4267,7 +4267,7 @@
         <v>40</v>
       </c>
       <c r="B132" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C132" t="n">
         <v>13.52</v>
@@ -4296,22 +4296,22 @@
         <v>40</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C133" t="n">
-        <v>6.93</v>
+        <v>8.05</v>
       </c>
       <c r="D133" t="n">
-        <v>16.43</v>
+        <v>16.82</v>
       </c>
       <c r="E133" t="n">
-        <v>4.86</v>
+        <v>1.82</v>
       </c>
       <c r="F133" t="n">
-        <v>0.11</v>
+        <v>0.07</v>
       </c>
       <c r="G133" t="n">
-        <v>-4.86</v>
+        <v>-1.82</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4325,25 +4325,25 @@
         <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C134" t="n">
-        <v>7.62</v>
+        <v>10.21</v>
       </c>
       <c r="D134" t="n">
-        <v>9.93</v>
+        <v>13.77</v>
       </c>
       <c r="E134" t="n">
-        <v>0.98</v>
+        <v>2.78</v>
       </c>
       <c r="F134" t="n">
-        <v>0.07</v>
+        <v>0.01</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.98</v>
+        <v>-2.78</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" t="s">
         <v>36</v>
@@ -4354,22 +4354,22 @@
         <v>41</v>
       </c>
       <c r="B135" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>16.2</v>
+        <v>11.73</v>
       </c>
       <c r="D135" t="n">
-        <v>20.69</v>
+        <v>15.01</v>
       </c>
       <c r="E135" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="F135" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="G135" t="n">
-        <v>-1.85</v>
+        <v>-2.46</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>41</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C136" t="n">
         <v>15.89</v>
@@ -4412,25 +4412,25 @@
         <v>41</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C137" t="n">
-        <v>10.47</v>
+        <v>7.66</v>
       </c>
       <c r="D137" t="n">
-        <v>13.55</v>
+        <v>9.9</v>
       </c>
       <c r="E137" t="n">
-        <v>2.29</v>
+        <v>1.02</v>
       </c>
       <c r="F137" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G137" t="n">
-        <v>-2.29</v>
+        <v>-1.02</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="s">
         <v>36</v>
@@ -4441,22 +4441,22 @@
         <v>41</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C138" t="n">
-        <v>16.54</v>
+        <v>16.2</v>
       </c>
       <c r="D138" t="n">
-        <v>20.79</v>
+        <v>20.69</v>
       </c>
       <c r="E138" t="n">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="F138" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G138" t="n">
-        <v>-2.53</v>
+        <v>-1.85</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4470,22 +4470,22 @@
         <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C139" t="n">
-        <v>10.21</v>
+        <v>16.54</v>
       </c>
       <c r="D139" t="n">
-        <v>13.77</v>
+        <v>20.79</v>
       </c>
       <c r="E139" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="F139" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="G139" t="n">
-        <v>-2.78</v>
+        <v>-2.53</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
         <v>42</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C140" t="n">
-        <v>71.22</v>
+        <v>27.09</v>
       </c>
       <c r="D140" t="n">
-        <v>28.25</v>
+        <v>16.65</v>
       </c>
       <c r="E140" t="n">
-        <v>6.98</v>
+        <v>2.15</v>
       </c>
       <c r="F140" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="G140" t="n">
-        <v>-6.98</v>
+        <v>-2.15</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4528,22 +4528,22 @@
         <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C141" t="n">
-        <v>30.24</v>
+        <v>66.51</v>
       </c>
       <c r="D141" t="n">
-        <v>18.68</v>
+        <v>27.62</v>
       </c>
       <c r="E141" t="n">
-        <v>3.17</v>
+        <v>3.88</v>
       </c>
       <c r="F141" t="n">
-        <v>0.51</v>
+        <v>0.01</v>
       </c>
       <c r="G141" t="n">
-        <v>-3.17</v>
+        <v>-3.88</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4557,25 +4557,25 @@
         <v>42</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C142" t="n">
-        <v>26.44</v>
+        <v>26.52</v>
       </c>
       <c r="D142" t="n">
-        <v>14.18</v>
+        <v>14.53</v>
       </c>
       <c r="E142" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="F142" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="G142" t="n">
-        <v>-2.03</v>
+        <v>-2.09</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" t="s">
         <v>36</v>
@@ -4586,25 +4586,25 @@
         <v>42</v>
       </c>
       <c r="B143" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C143" t="n">
-        <v>27.21</v>
+        <v>26.44</v>
       </c>
       <c r="D143" t="n">
-        <v>16.4</v>
+        <v>14.18</v>
       </c>
       <c r="E143" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="F143" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="G143" t="n">
-        <v>-2.34</v>
+        <v>-2.03</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="s">
         <v>36</v>
@@ -4615,22 +4615,22 @@
         <v>42</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C144" t="n">
-        <v>26.52</v>
+        <v>27.21</v>
       </c>
       <c r="D144" t="n">
-        <v>14.53</v>
+        <v>16.4</v>
       </c>
       <c r="E144" t="n">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="F144" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="G144" t="n">
-        <v>-2.09</v>
+        <v>-2.34</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4647,19 +4647,19 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>27.09</v>
+        <v>31.99</v>
       </c>
       <c r="D145" t="n">
-        <v>16.65</v>
+        <v>19.27</v>
       </c>
       <c r="E145" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="F145" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="G145" t="n">
-        <v>-2.15</v>
+        <v>-3.12</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>

--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -482,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -499,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>7.48</v>
+        <v>7.44</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.84</v>
+        <v>-1.3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-13.43</v>
+        <v>-11.78</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.1</v>
+        <v>-2.79</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -567,7 +567,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5.44</v>
+        <v>5.53</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.07</v>
+        <v>-0.61</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.91</v>
+        <v>1.92</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -635,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.87</v>
+        <v>0.63</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.19</v>
+        <v>-0.82</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.75</v>
+        <v>-2.31</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>-4.12</v>
+        <v>-4.02</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>3.72</v>
+        <v>3.99</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-3.98</v>
+        <v>-4.78</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>8.64</v>
+        <v>9.16</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.64</v>
+        <v>-2.57</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.61</v>
+        <v>-1.1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>-11.78</v>
+        <v>-12.1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>3.33</v>
+        <v>3.67</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>5.07</v>
+        <v>4.85</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>-10.52</v>
+        <v>-11.78</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.43</v>
+        <v>0.07</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>8.07</v>
+        <v>8.35</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.45</v>
+        <v>-0.07</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>-13.48</v>
+        <v>-14.08</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="n">
-        <v>4.53</v>
+        <v>4.06</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>-5.97</v>
+        <v>-6.06</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>3.36</v>
+        <v>4.03</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>1.32</v>
+        <v>0.02</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>-8.76</v>
+        <v>-8.79</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>6.59</v>
+        <v>6.98</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>-3.03</v>
+        <v>-4.09</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.05</v>
+        <v>-0.94</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>8.19</v>
+        <v>9.07</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.73</v>
+        <v>-5.9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>11</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.61</v>
+        <v>-0.18</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>12</v>
       </c>
       <c r="C49" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>-3.38</v>
+        <v>-3.3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.61</v>
+        <v>-1.53</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1349,7 +1349,7 @@
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.77</v>
+        <v>-1.1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.03</v>
+        <v>-0.9</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>6.98</v>
+        <v>6.92</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1417,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>-6.5</v>
+        <v>-5.69</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.58</v>
+        <v>-2.12</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>3.63</v>
+        <v>3.87</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>-4.55</v>
+        <v>-3.89</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>6</v>
       </c>
       <c r="C62" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>-14.23</v>
+        <v>-14.37</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="C66" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>4.93</v>
+        <v>4.92</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.1</v>
+        <v>-8.44</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.79</v>
+        <v>-1.25</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>5.58</v>
+        <v>5.29</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -1655,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>-2.18</v>
+        <v>0.19</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>2.73</v>
+        <v>2.31</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>2.76</v>
+        <v>1.92</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>6</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.64</v>
+        <v>-1.81</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>5.34</v>
+        <v>5.12</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>2.42</v>
+        <v>3.48</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>-8.47</v>
+        <v>-9.57</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>11</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.67</v>
+        <v>-1.24</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>-5.66</v>
+        <v>-4.77</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1859,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>-6.29</v>
+        <v>-7.83</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>2.87</v>
+        <v>3.01</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>-6.56</v>
+        <v>-8.25</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="C90" t="n">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="C91" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>6</v>
       </c>
       <c r="C92" t="n">
-        <v>10.05</v>
+        <v>10.3</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="n">
-        <v>6.36</v>
+        <v>6.27</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>-12.36</v>
+        <v>-12.09</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.39</v>
+        <v>-7.63</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>12</v>
       </c>
       <c r="C97" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.87</v>
+        <v>-0.83</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.38</v>
+        <v>-6.9</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>11</v>
       </c>
       <c r="C102" t="n">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>-14.65</v>
+        <v>-14.45</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="C105" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>2.03</v>
+        <v>0.39</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>6.6</v>
+        <v>7.24</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.83</v>
+        <v>-1.8</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="C111" t="n">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>-7</v>
+        <v>-6.72</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>11</v>
       </c>
       <c r="C114" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>12</v>
       </c>
       <c r="C115" t="n">
-        <v>5.12</v>
+        <v>4.99</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="C116" t="n">
-        <v>-2.64</v>
+        <v>-2.61</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>-12.32</v>
+        <v>-12.33</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>11</v>
       </c>
       <c r="C120" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>8.06</v>
+        <v>7.9</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -2522,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>-10.38</v>
+        <v>-10.6</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>6.77</v>
+        <v>6.97</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>4.99</v>
+        <v>4.34</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>-4.95</v>
+        <v>-4.46</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>-12.9</v>
+        <v>-12.85</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>-3.53</v>
+        <v>-3.76</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>4.86</v>
+        <v>4.21</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>10.53</v>
+        <v>10.81</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>4.69</v>
+        <v>5.06</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>-3.65</v>
+        <v>-3.47</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>-13.2</v>
+        <v>-13.37</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>5.86</v>
+        <v>5.9</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="C137" t="n">
-        <v>-6.55</v>
+        <v>-6.39</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.47</v>
+        <v>-0.27</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>-4.44</v>
+        <v>-3.9</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>-6.73</v>
+        <v>-7.23</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>9.85</v>
+        <v>9.8</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>

--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -482,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -499,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>7.44</v>
+        <v>7.31</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.78</v>
+        <v>-11.88</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.79</v>
+        <v>-2.94</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -567,7 +567,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5.53</v>
+        <v>5.41</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.61</v>
+        <v>-0.73</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -635,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.82</v>
+        <v>-0.75</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.31</v>
+        <v>-2.48</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>-4.02</v>
+        <v>-3.99</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>3.99</v>
+        <v>3.91</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -771,7 +771,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.57</v>
+        <v>-2.56</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>4.85</v>
+        <v>4.84</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>8.35</v>
+        <v>8.41</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.07</v>
+        <v>-0.69</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>-14.08</v>
+        <v>-13.89</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.06</v>
+        <v>-6.07</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>-8.79</v>
+        <v>-8.8</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>6.98</v>
+        <v>6.96</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.94</v>
+        <v>-0.95</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.9</v>
+        <v>-5.91</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>-3.3</v>
+        <v>-3.31</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.53</v>
+        <v>-1.54</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>4.79</v>
+        <v>4.84</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1349,7 +1349,7 @@
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>-1.1</v>
+        <v>-1.12</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>6.92</v>
+        <v>6.94</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1417,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>-5.69</v>
+        <v>-5.7</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.12</v>
+        <v>-2.13</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>-3.89</v>
+        <v>-3.9</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>-14.37</v>
+        <v>-14.36</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -1655,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>6</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.81</v>
+        <v>-1.82</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>11</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.24</v>
+        <v>-1.25</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="C79" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>-4.77</v>
+        <v>-4.76</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1859,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.83</v>
+        <v>-7.86</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.63</v>
+        <v>-7.62</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>-6.9</v>
+        <v>-6.95</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>11</v>
       </c>
       <c r="C102" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="C105" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.8</v>
+        <v>-1.79</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="C111" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>-6.72</v>
+        <v>-6.7</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>11</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>12</v>
       </c>
       <c r="C115" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="C116" t="n">
-        <v>-2.61</v>
+        <v>-2.64</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>-12.33</v>
+        <v>-12.38</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>11</v>
       </c>
       <c r="C120" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>7.9</v>
+        <v>7.87</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -2522,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>-10.6</v>
+        <v>-10.61</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>6.97</v>
+        <v>6.89</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>4.34</v>
+        <v>4.56</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>-4.46</v>
+        <v>-4.52</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>-12.85</v>
+        <v>-12.82</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>-3.76</v>
+        <v>-3.77</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>10.81</v>
+        <v>10.78</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>-3.47</v>
+        <v>-3.48</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>-13.37</v>
+        <v>-13.36</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>-3.9</v>
+        <v>-3.88</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.23</v>
+        <v>-7.22</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.6</v>
+        <v>-0.58</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>9.8</v>
+        <v>9.82</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>

--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Genital herpes</t>
   </si>
   <si>
-    <t xml:space="preserve">CA</t>
+    <t xml:space="preserve">CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">HBV</t>
@@ -482,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -499,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>7.31</v>
+        <v>7.36</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.7</v>
+        <v>-0.85</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.88</v>
+        <v>-11.86</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.94</v>
+        <v>-2.91</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -567,7 +567,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.73</v>
+        <v>-0.62</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -635,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.75</v>
+        <v>-0.83</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.48</v>
+        <v>-2.32</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>-3.99</v>
+        <v>-4.03</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-4.78</v>
+        <v>-4.79</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.56</v>
+        <v>-2.58</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.13</v>
+        <v>-1.08</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>4.84</v>
+        <v>4.43</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>-11.78</v>
+        <v>-11.74</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>8.41</v>
+        <v>8.38</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.69</v>
+        <v>-0.34</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>-13.89</v>
+        <v>-14</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="n">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.07</v>
+        <v>-6.06</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>6.96</v>
+        <v>6.92</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.95</v>
+        <v>-0.94</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>9.07</v>
+        <v>9.04</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.91</v>
+        <v>-5.89</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>11</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>12</v>
       </c>
       <c r="C49" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1349,7 +1349,7 @@
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>-1.12</v>
+        <v>-1.11</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1417,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>-5.7</v>
+        <v>-5.69</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>-3.9</v>
+        <v>-3.88</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>6</v>
       </c>
       <c r="C62" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>-14.36</v>
+        <v>-14.38</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="C66" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.44</v>
+        <v>-8.43</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>5.23</v>
+        <v>5.24</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -1672,7 +1672,7 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>-9.57</v>
+        <v>-9.56</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>-4.76</v>
+        <v>-4.75</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>3.88</v>
+        <v>3.73</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1859,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.86</v>
+        <v>-7.81</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>-8.25</v>
+        <v>-8.26</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>-6.95</v>
+        <v>-6.91</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>11</v>
       </c>
       <c r="C102" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>-14.45</v>
+        <v>-14.48</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="C105" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>7.23</v>
+        <v>7.19</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.79</v>
+        <v>-1.82</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="C111" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>-6.7</v>
+        <v>-6.76</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>11</v>
       </c>
       <c r="C114" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>12</v>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>-12.38</v>
+        <v>-12.37</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>-10.61</v>
+        <v>-10.67</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>6.89</v>
+        <v>6.71</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>4.56</v>
+        <v>5.12</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>-4.52</v>
+        <v>-4.64</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>-12.82</v>
+        <v>-12.8</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>-3.77</v>
+        <v>-3.81</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>4.24</v>
+        <v>4.43</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>10.78</v>
+        <v>10.69</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>-3.48</v>
+        <v>-3.51</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>-13.36</v>
+        <v>-13.33</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>5.9</v>
+        <v>5.98</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="n">
-        <v>3.03</v>
+        <v>2.72</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="C137" t="n">
-        <v>-6.39</v>
+        <v>-6.34</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>6.54</v>
+        <v>6.62</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>-3.88</v>
+        <v>-3.9</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.22</v>
+        <v>-7.23</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.58</v>
+        <v>-0.6</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>9.82</v>
+        <v>9.8</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>

--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -482,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -499,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>7.36</v>
+        <v>7.28</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.85</v>
+        <v>-0.43</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.86</v>
+        <v>-11.97</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.91</v>
+        <v>-3.01</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -567,7 +567,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5.44</v>
+        <v>5.37</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -635,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.83</v>
+        <v>-0.85</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.32</v>
+        <v>-2.33</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>-4.03</v>
+        <v>-4.02</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-4.79</v>
+        <v>-4.8</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.58</v>
+        <v>-2.56</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.08</v>
+        <v>-1.13</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>4.43</v>
+        <v>4.84</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>-11.74</v>
+        <v>-11.77</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0.18</v>
+        <v>0.07</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>8.38</v>
+        <v>8.42</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.34</v>
+        <v>-0.88</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="n">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>-8.8</v>
+        <v>-8.79</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>6.92</v>
+        <v>6.97</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>9.04</v>
+        <v>9.06</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.89</v>
+        <v>-5.9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>6.93</v>
+        <v>6.92</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>-3.88</v>
+        <v>-3.89</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>6</v>
       </c>
       <c r="C62" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>-14.38</v>
+        <v>-14.37</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="C66" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.43</v>
+        <v>-8.44</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>-9.56</v>
+        <v>-9.57</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>-4.75</v>
+        <v>-4.78</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>3.73</v>
+        <v>4.01</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1859,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.81</v>
+        <v>-7.9</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>-8.26</v>
+        <v>-8.25</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="C91" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.62</v>
+        <v>-7.63</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.79</v>
+        <v>-0.73</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>-6.91</v>
+        <v>-6.84</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>11</v>
       </c>
       <c r="C102" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>-14.48</v>
+        <v>-14.49</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="C105" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>7.19</v>
+        <v>7.2</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.82</v>
+        <v>-1.81</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="C111" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>-6.76</v>
+        <v>-6.77</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>11</v>
       </c>
       <c r="C114" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>-12.37</v>
+        <v>-12.38</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>-10.67</v>
+        <v>-10.64</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>6.71</v>
+        <v>6.79</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.12</v>
+        <v>4.84</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>-4.64</v>
+        <v>-4.59</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>-12.8</v>
+        <v>-12.84</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>-3.81</v>
+        <v>-3.78</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>10.69</v>
+        <v>10.76</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>-3.51</v>
+        <v>-3.49</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>-13.33</v>
+        <v>-13.34</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>5.98</v>
+        <v>5.94</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="C137" t="n">
-        <v>-6.34</v>
+        <v>-6.37</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>6.62</v>
+        <v>6.58</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>-3.9</v>
+        <v>-3.89</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>9.8</v>
+        <v>9.81</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>

--- a/Outcome/Appendix/Best_model_outcome.xlsx
+++ b/Outcome/Appendix/Best_model_outcome.xlsx
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.43</v>
+        <v>-0.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.97</v>
+        <v>-11.96</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.01</v>
+        <v>-3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -635,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.85</v>
+        <v>-0.87</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.33</v>
+        <v>-2.32</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>-4.02</v>
+        <v>-4.01</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-4.8</v>
+        <v>-4.79</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.56</v>
+        <v>-2.57</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.13</v>
+        <v>-1.1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>-12.1</v>
+        <v>-12.09</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>-11.77</v>
+        <v>-11.78</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>8.42</v>
+        <v>8.46</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.88</v>
+        <v>-1.07</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.06</v>
+        <v>-6.07</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>-8.79</v>
+        <v>-8.81</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>6.97</v>
+        <v>6.9</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>-4.09</v>
+        <v>-4.07</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>9.06</v>
+        <v>9.05</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.9</v>
+        <v>-5.92</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>12</v>
       </c>
       <c r="C49" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>6</v>
       </c>
       <c r="C62" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>-14.37</v>
+        <v>-14.38</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="C66" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -1621,7 +1621,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="n">
-        <v>-1.25</v>
+        <v>-1.26</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -1655,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>-9.57</v>
+        <v>-9.55</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>-4.78</v>
+        <v>-4.73</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>4.01</v>
+        <v>3.58</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1859,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.9</v>
+        <v>-7.76</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>-8.25</v>
+        <v>-8.26</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="C90" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="C91" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="n">
-        <v>6.27</v>
+        <v>6.28</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>-12.09</v>
+        <v>-12.08</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.63</v>
+        <v>-7.62</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>-6.84</v>
+        <v>-6.98</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>11</v>
       </c>
       <c r="C102" t="n">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>-14.49</v>
+        <v>-14.47</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>7.2</v>
+        <v>7.21</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.81</v>
+        <v>-1.79</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="C111" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>-6.77</v>
+        <v>-6.7</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>11</v>
       </c>
       <c r="C114" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>12</v>
       </c>
       <c r="C115" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="C116" t="n">
-        <v>-2.64</v>
+        <v>-2.67</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>-12.38</v>
+        <v>-12.41</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>11</v>
       </c>
       <c r="C120" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>7.87</v>
+        <v>7.84</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -2522,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>-10.64</v>
+        <v>-10.67</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>6.79</v>
+        <v>6.71</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>4.84</v>
+        <v>5.09</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>-4.59</v>
+        <v>-4.63</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>-12.84</v>
+        <v>-12.83</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>-3.78</v>
+        <v>-3.77</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>10.76</v>
+        <v>10.78</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>5.03</v>
+        <v>5.06</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>-3.49</v>
+        <v>-3.48</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>-13.34</v>
+        <v>-13.36</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>5.94</v>
+        <v>5.92</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>6.58</v>
+        <v>6.56</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>-3.89</v>
+        <v>-3.88</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.23</v>
+        <v>-7.22</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.59</v>
+        <v>-0.58</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
